--- a/results/Int Task Remove ACC -0.5/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_1_permute.xlsx
@@ -440,347 +440,347 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6770142199957784</v>
+        <v>0.6799855140603532</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6746302503911051</v>
+        <v>0.6792093999346189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7006079751155789</v>
+        <v>0.6662577811441988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6986414002211373</v>
+        <v>0.6662577811441988</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7032807490930095</v>
+        <v>0.6581297287905955</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7038695975865403</v>
+        <v>0.6545251987530357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7035680294321375</v>
+        <v>0.6545251987530357</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7023331811839759</v>
+        <v>0.6798298721259584</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.698844477702245</v>
+        <v>0.6855739548748883</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6647228887752638</v>
+        <v>0.6967620762519746</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6584914962733568</v>
+        <v>0.6988873411480698</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6584914962733568</v>
+        <v>0.6451638221849003</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6603422446119696</v>
+        <v>0.6414021261793162</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6703383811867193</v>
+        <v>0.6366372350372282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6705669862311182</v>
+        <v>0.630978879179948</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6663736077000275</v>
+        <v>0.6285316621796576</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6576408950039891</v>
+        <v>0.6218287717736779</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6475095004446368</v>
+        <v>0.6003077023897609</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6458873571504229</v>
+        <v>0.5939477195503796</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6397860790196197</v>
+        <v>0.6113580892275969</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6190778910727444</v>
+        <v>0.6008935028160332</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6178430428245829</v>
+        <v>0.6026600482966258</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.614554368756701</v>
+        <v>0.6122469818419013</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6154590732199097</v>
+        <v>0.6068345669115535</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6040091990669866</v>
+        <v>0.5911545469162323</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6046694866368921</v>
+        <v>0.5886118873099054</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5808741780696133</v>
+        <v>0.5752142981787036</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5905453144729091</v>
+        <v>0.5721700410041248</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5893961931163973</v>
+        <v>0.5750571322106793</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.559128123221167</v>
+        <v>0.5788331160315383</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5533840404722371</v>
+        <v>0.5788331160315383</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5595679974274312</v>
+        <v>0.5801108277255246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5595679974274312</v>
+        <v>0.5779426993836045</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5592521414577534</v>
+        <v>0.5481154562156568</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5595394217968813</v>
+        <v>0.5449711843341535</v>
       </c>
     </row>
     <row r="37">
@@ -790,67 +790,67 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.567162828514974</v>
+        <v>0.5255309923668776</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5577953558123214</v>
+        <v>0.537723832914097</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5535019625743062</v>
+        <v>0.537723832914097</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5571937435371449</v>
+        <v>0.537723832914097</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.525583190518682</v>
+        <v>0.5481200283165448</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5461612640944535</v>
+        <v>0.5382886778779661</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5461612640944535</v>
+        <v>0.5324573442037572</v>
       </c>
     </row>
     <row r="44">
@@ -860,217 +860,217 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5439216966761589</v>
+        <v>0.5321414882340794</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5448406889546424</v>
+        <v>0.5482373789060029</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5418250074106135</v>
+        <v>0.5469882428425665</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5455280281214685</v>
+        <v>0.5763041727278755</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5361493156707996</v>
+        <v>0.5537151367782082</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5323432321857614</v>
+        <v>0.5600894074328644</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5315814058753021</v>
+        <v>0.5597878392784615</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5247024895851352</v>
+        <v>0.5605593813033078</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5224756859484861</v>
+        <v>0.5173101644660891</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5526039257582258</v>
+        <v>0.526698592631145</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5531927742517566</v>
+        <v>0.4846352644617456</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5450887254278153</v>
+        <v>0.5003632915163906</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5450887254278153</v>
+        <v>0.5060201233400416</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5407223690797961</v>
+        <v>0.5063216914944445</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5420429442196072</v>
+        <v>0.5031473199487619</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5384812776278721</v>
+        <v>0.5031473199487619</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.548434550756797</v>
+        <v>0.4951621457479081</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5335704602657763</v>
+        <v>0.4942002900235997</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5256995885871217</v>
+        <v>0.4911861325132</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5129382834961635</v>
+        <v>0.4933685486703949</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5267435516232102</v>
+        <v>0.4875575989459783</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5197345209619395</v>
+        <v>0.4853736587551541</v>
       </c>
     </row>
     <row r="66">
@@ -1080,247 +1080,247 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5400967532749578</v>
+        <v>0.4953366475984659</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4968949719844518</v>
+        <v>0.4960397986141962</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4965934038300489</v>
+        <v>0.4974619124945611</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4879479420592895</v>
+        <v>0.4966000714771772</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4894700706465789</v>
+        <v>0.4979206466169883</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5054404190482867</v>
+        <v>0.4968016249246556</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4945110023797785</v>
+        <v>0.4941033233839338</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5004250148783783</v>
+        <v>0.5080101302515342</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4976808018245731</v>
+        <v>0.5060721309876424</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4976808018245731</v>
+        <v>0.4745257778858148</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4908575127618766</v>
+        <v>0.4740740924189233</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4946493084316398</v>
+        <v>0.4749614609995984</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4929955414396174</v>
+        <v>0.4755503094931293</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4689348605166322</v>
+        <v>0.4984348174626821</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4986222735990892</v>
+        <v>0.4867910100304274</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4986222735990892</v>
+        <v>0.515945201846824</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.5247381138712207</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.5253126745494766</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.5168615270664563</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.5217346245962263</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.5220535286331628</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5133019560209615</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.5118272629803849</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.500272992523853</v>
+        <v>0.5115542704565319</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5005888484935309</v>
+        <v>0.50280993700407</v>
       </c>
     </row>
   </sheetData>
